--- a/storage/templates/Bar_Piscina.xlsx
+++ b/storage/templates/Bar_Piscina.xlsx
@@ -320,7 +320,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -426,6 +426,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7614,8 +7617,10 @@
       </c>
     </row>
     <row r="103" ht="25.05" customHeight="1">
-      <c r="A103" s="3" t="n">
-        <v>58</v>
+      <c r="A103" s="37" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>

--- a/storage/templates/Bar_Piscina.xlsx
+++ b/storage/templates/Bar_Piscina.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN1001"/>
+  <dimension ref="A1:AN1005"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="1" min="1" max="1"/>
@@ -7686,54 +7686,322 @@
         <v/>
       </c>
     </row>
-    <row r="104" ht="22.05" customHeight="1">
-      <c r="C104" s="11">
-        <f>SUM(C7:C103)</f>
-        <v/>
-      </c>
-      <c r="D104" s="12" t="n"/>
-      <c r="E104" s="13" t="inlineStr">
+    <row r="104" ht="25.05" customHeight="1">
+      <c r="A104" s="37" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>APERITIVO MARTINI BLANCO SECO 100 CL</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>8.42225</v>
+      </c>
+      <c r="F104" s="10">
+        <f>C104*E104</f>
+        <v/>
+      </c>
+      <c r="G104" s="22" t="n"/>
+      <c r="H104" s="22" t="n"/>
+      <c r="I104" s="22" t="n"/>
+      <c r="J104" s="22" t="n"/>
+      <c r="K104" s="22" t="n"/>
+      <c r="L104" s="22" t="n"/>
+      <c r="M104" s="22" t="n"/>
+      <c r="N104" s="22" t="n"/>
+      <c r="O104" s="22" t="n"/>
+      <c r="P104" s="22" t="n"/>
+      <c r="Q104" s="22" t="n"/>
+      <c r="R104" s="22" t="n"/>
+      <c r="S104" s="22" t="n"/>
+      <c r="T104" s="22" t="n"/>
+      <c r="U104" s="22" t="n"/>
+      <c r="V104" s="22" t="n"/>
+      <c r="W104" s="22" t="n"/>
+      <c r="X104" s="22" t="n"/>
+      <c r="Y104" s="22" t="n"/>
+      <c r="Z104" s="22" t="n"/>
+      <c r="AA104" s="22" t="n"/>
+      <c r="AB104" s="22" t="n"/>
+      <c r="AC104" s="22" t="n"/>
+      <c r="AD104" s="22" t="n"/>
+      <c r="AE104" s="22" t="n"/>
+      <c r="AF104" s="22" t="n"/>
+      <c r="AG104" s="22" t="n"/>
+      <c r="AH104" s="22" t="n"/>
+      <c r="AI104" s="22" t="n"/>
+      <c r="AJ104" s="22" t="n"/>
+      <c r="AK104" s="22" t="n"/>
+      <c r="AL104" s="23">
+        <f>SUM(G104:AK104)</f>
+        <v/>
+      </c>
+      <c r="AM104" s="24">
+        <f>SUM(C104,AL104)</f>
+        <v/>
+      </c>
+      <c r="AN104" s="25">
+        <f>E104*AM104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="25.05" customHeight="1">
+      <c r="A105" s="37" t="inlineStr">
+        <is>
+          <t>28190</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>BIB COCKTAIL DAIQUIRI LIMON C/ALCOHOL FROZEN</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>LITRO</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>10.1637</v>
+      </c>
+      <c r="F105" s="10">
+        <f>C105*E105</f>
+        <v/>
+      </c>
+      <c r="G105" s="22" t="n"/>
+      <c r="H105" s="22" t="n"/>
+      <c r="I105" s="22" t="n"/>
+      <c r="J105" s="22" t="n"/>
+      <c r="K105" s="22" t="n"/>
+      <c r="L105" s="22" t="n"/>
+      <c r="M105" s="22" t="n"/>
+      <c r="N105" s="22" t="n"/>
+      <c r="O105" s="22" t="n"/>
+      <c r="P105" s="22" t="n"/>
+      <c r="Q105" s="22" t="n"/>
+      <c r="R105" s="22" t="n"/>
+      <c r="S105" s="22" t="n"/>
+      <c r="T105" s="22" t="n"/>
+      <c r="U105" s="22" t="n"/>
+      <c r="V105" s="22" t="n"/>
+      <c r="W105" s="22" t="n"/>
+      <c r="X105" s="22" t="n"/>
+      <c r="Y105" s="22" t="n"/>
+      <c r="Z105" s="22" t="n"/>
+      <c r="AA105" s="22" t="n"/>
+      <c r="AB105" s="22" t="n"/>
+      <c r="AC105" s="22" t="n"/>
+      <c r="AD105" s="22" t="n"/>
+      <c r="AE105" s="22" t="n"/>
+      <c r="AF105" s="22" t="n"/>
+      <c r="AG105" s="22" t="n"/>
+      <c r="AH105" s="22" t="n"/>
+      <c r="AI105" s="22" t="n"/>
+      <c r="AJ105" s="22" t="n"/>
+      <c r="AK105" s="22" t="n"/>
+      <c r="AL105" s="23">
+        <f>SUM(G105:AK105)</f>
+        <v/>
+      </c>
+      <c r="AM105" s="24">
+        <f>SUM(C105,AL105)</f>
+        <v/>
+      </c>
+      <c r="AN105" s="25">
+        <f>E105*AM105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="25.05" customHeight="1">
+      <c r="A106" s="37" t="inlineStr">
+        <is>
+          <t>4107</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>WHISKY DEWARS WHITE LABEL 70 CL</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>10.82118</v>
+      </c>
+      <c r="F106" s="10">
+        <f>C106*E106</f>
+        <v/>
+      </c>
+      <c r="G106" s="22" t="n"/>
+      <c r="H106" s="22" t="n"/>
+      <c r="I106" s="22" t="n"/>
+      <c r="J106" s="22" t="n"/>
+      <c r="K106" s="22" t="n"/>
+      <c r="L106" s="22" t="n"/>
+      <c r="M106" s="22" t="n"/>
+      <c r="N106" s="22" t="n"/>
+      <c r="O106" s="22" t="n"/>
+      <c r="P106" s="22" t="n"/>
+      <c r="Q106" s="22" t="n"/>
+      <c r="R106" s="22" t="n"/>
+      <c r="S106" s="22" t="n"/>
+      <c r="T106" s="22" t="n"/>
+      <c r="U106" s="22" t="n"/>
+      <c r="V106" s="22" t="n"/>
+      <c r="W106" s="22" t="n"/>
+      <c r="X106" s="22" t="n"/>
+      <c r="Y106" s="22" t="n"/>
+      <c r="Z106" s="22" t="n"/>
+      <c r="AA106" s="22" t="n"/>
+      <c r="AB106" s="22" t="n"/>
+      <c r="AC106" s="22" t="n"/>
+      <c r="AD106" s="22" t="n"/>
+      <c r="AE106" s="22" t="n"/>
+      <c r="AF106" s="22" t="n"/>
+      <c r="AG106" s="22" t="n"/>
+      <c r="AH106" s="22" t="n"/>
+      <c r="AI106" s="22" t="n"/>
+      <c r="AJ106" s="22" t="n"/>
+      <c r="AK106" s="22" t="n"/>
+      <c r="AL106" s="23">
+        <f>SUM(G106:AK106)</f>
+        <v/>
+      </c>
+      <c r="AM106" s="24">
+        <f>SUM(C106,AL106)</f>
+        <v/>
+      </c>
+      <c r="AN106" s="25">
+        <f>E106*AM106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="25.05" customHeight="1">
+      <c r="A107" s="37" t="inlineStr">
+        <is>
+          <t>30756</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>AZUCAR TERRON BLANCO 4 GR</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>UNIDAD</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>0.01037</v>
+      </c>
+      <c r="F107" s="10">
+        <f>C107*E107</f>
+        <v/>
+      </c>
+      <c r="G107" s="22" t="n"/>
+      <c r="H107" s="22" t="n"/>
+      <c r="I107" s="22" t="n"/>
+      <c r="J107" s="22" t="n"/>
+      <c r="K107" s="22" t="n"/>
+      <c r="L107" s="22" t="n"/>
+      <c r="M107" s="22" t="n"/>
+      <c r="N107" s="22" t="n"/>
+      <c r="O107" s="22" t="n"/>
+      <c r="P107" s="22" t="n"/>
+      <c r="Q107" s="22" t="n"/>
+      <c r="R107" s="22" t="n"/>
+      <c r="S107" s="22" t="n"/>
+      <c r="T107" s="22" t="n"/>
+      <c r="U107" s="22" t="n"/>
+      <c r="V107" s="22" t="n"/>
+      <c r="W107" s="22" t="n"/>
+      <c r="X107" s="22" t="n"/>
+      <c r="Y107" s="22" t="n"/>
+      <c r="Z107" s="22" t="n"/>
+      <c r="AA107" s="22" t="n"/>
+      <c r="AB107" s="22" t="n"/>
+      <c r="AC107" s="22" t="n"/>
+      <c r="AD107" s="22" t="n"/>
+      <c r="AE107" s="22" t="n"/>
+      <c r="AF107" s="22" t="n"/>
+      <c r="AG107" s="22" t="n"/>
+      <c r="AH107" s="22" t="n"/>
+      <c r="AI107" s="22" t="n"/>
+      <c r="AJ107" s="22" t="n"/>
+      <c r="AK107" s="22" t="n"/>
+      <c r="AL107" s="23">
+        <f>SUM(G107:AK107)</f>
+        <v/>
+      </c>
+      <c r="AM107" s="24">
+        <f>SUM(C107,AL107)</f>
+        <v/>
+      </c>
+      <c r="AN107" s="25">
+        <f>E107*AM107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="22.05" customHeight="1">
+      <c r="C108" s="11">
+        <f>SUM(C7:C107)</f>
+        <v/>
+      </c>
+      <c r="D108" s="12" t="n"/>
+      <c r="E108" s="13" t="inlineStr">
         <is>
           <t>ESTOCAJE  INICIAL</t>
         </is>
       </c>
-      <c r="F104" s="14">
-        <f>SUM(F7:F103)</f>
-        <v/>
-      </c>
-      <c r="AL104" s="11">
-        <f>SUM(AL7:AL103)</f>
-        <v/>
-      </c>
-      <c r="AM104" s="24">
-        <f>SUM(AM7:AM103)</f>
-        <v/>
-      </c>
-      <c r="AN104" s="26">
-        <f>SUM(AN7:AN103)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" ht="22.05" customHeight="1">
-      <c r="E105" s="3" t="n"/>
-      <c r="F105" s="3" t="n"/>
-      <c r="AN105" s="21" t="n"/>
-    </row>
-    <row r="106" ht="22.05" customHeight="1">
-      <c r="E106" s="3" t="n"/>
-      <c r="F106" s="3" t="n"/>
-      <c r="AN106" s="21" t="n"/>
-    </row>
-    <row r="107" ht="22.05" customHeight="1">
-      <c r="AN107" s="21" t="n"/>
-    </row>
-    <row r="108" ht="22.05" customHeight="1">
-      <c r="AN108" s="21" t="n"/>
+      <c r="F108" s="14">
+        <f>SUM(F7:F107)</f>
+        <v/>
+      </c>
+      <c r="AL108" s="11">
+        <f>SUM(AL7:AL107)</f>
+        <v/>
+      </c>
+      <c r="AM108" s="24">
+        <f>SUM(AM7:AM107)</f>
+        <v/>
+      </c>
+      <c r="AN108" s="26">
+        <f>SUM(AN7:AN107)</f>
+        <v/>
+      </c>
     </row>
     <row r="109" ht="22.05" customHeight="1">
+      <c r="E109" s="3" t="n"/>
+      <c r="F109" s="3" t="n"/>
       <c r="AN109" s="21" t="n"/>
     </row>
     <row r="110" ht="22.05" customHeight="1">
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="n"/>
       <c r="AN110" s="21" t="n"/>
     </row>
     <row r="111" ht="22.05" customHeight="1">
@@ -10408,6 +10676,18 @@
     </row>
     <row r="1001">
       <c r="AN1001" s="21" t="n"/>
+    </row>
+    <row r="1002">
+      <c r="AN1002" s="21" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="AN1003" s="21" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="AN1004" s="21" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="AN1005" s="21" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:F6"/>

--- a/storage/templates/Bar_Piscina.xlsx
+++ b/storage/templates/Bar_Piscina.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -51,10 +51,6 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial Black"/>
@@ -169,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -242,17 +238,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -273,15 +258,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -305,22 +286,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -340,7 +312,7 @@
     <xf numFmtId="4" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,10 +327,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -367,19 +339,19 @@
     <xf numFmtId="4" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -388,45 +360,33 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="9" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -759,7 +719,8 @@
     <col width="25.77734375" customWidth="1" style="1" min="38" max="38"/>
     <col width="40.77734375" customWidth="1" style="1" min="39" max="39"/>
     <col width="15.77734375" customWidth="1" style="1" min="40" max="40"/>
-    <col width="14.44140625" customWidth="1" style="1" min="41" max="16384"/>
+    <col width="14.44140625" customWidth="1" style="1" min="41" max="41"/>
+    <col width="14.44140625" customWidth="1" style="1" min="42" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.05" customHeight="1">
@@ -942,19 +903,19 @@
           <t>V</t>
         </is>
       </c>
-      <c r="AL5" s="32" t="inlineStr">
+      <c r="AL5" s="28" t="inlineStr">
         <is>
           <t>EXTRACION
   MENSUAL</t>
         </is>
       </c>
-      <c r="AM5" s="33" t="inlineStr">
+      <c r="AM5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">suma  stok inicial
 +  estracion mensual   </t>
         </is>
       </c>
-      <c r="AN5" s="34" t="inlineStr">
+      <c r="AN5" s="30" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
@@ -1084,9 +1045,9 @@
       <c r="AK6" s="20" t="n">
         <v>31</v>
       </c>
-      <c r="AL6" s="35" t="n"/>
-      <c r="AM6" s="35" t="n"/>
-      <c r="AN6" s="36" t="n"/>
+      <c r="AL6" s="29" t="n"/>
+      <c r="AM6" s="29" t="n"/>
+      <c r="AN6" s="31" t="n"/>
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -7617,7 +7578,7 @@
       </c>
     </row>
     <row r="103" ht="25.05" customHeight="1">
-      <c r="A103" s="37" t="inlineStr">
+      <c r="A103" s="27" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -7687,7 +7648,7 @@
       </c>
     </row>
     <row r="104" ht="25.05" customHeight="1">
-      <c r="A104" s="37" t="inlineStr">
+      <c r="A104" s="27" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -7757,7 +7718,7 @@
       </c>
     </row>
     <row r="105" ht="25.05" customHeight="1">
-      <c r="A105" s="37" t="inlineStr">
+      <c r="A105" s="27" t="inlineStr">
         <is>
           <t>28190</t>
         </is>
@@ -7827,7 +7788,7 @@
       </c>
     </row>
     <row r="106" ht="25.05" customHeight="1">
-      <c r="A106" s="37" t="inlineStr">
+      <c r="A106" s="27" t="inlineStr">
         <is>
           <t>4107</t>
         </is>
@@ -7897,12 +7858,12 @@
       </c>
     </row>
     <row r="107" ht="25.05" customHeight="1">
-      <c r="A107" s="37" t="inlineStr">
+      <c r="A107" s="27" t="inlineStr">
         <is>
           <t>30756</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B107" s="27" t="inlineStr">
         <is>
           <t>AZUCAR TERRON BLANCO 4 GR</t>
         </is>
@@ -7910,7 +7871,7 @@
       <c r="C107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D107" s="33" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
@@ -9390,7 +9351,7 @@
     <row r="572" ht="22.05" customHeight="1">
       <c r="AN572" s="21" t="n"/>
     </row>
-    <row r="573" ht="22.05" customHeight="1">
+    <row r="573" ht="15.75" customHeight="1">
       <c r="AN573" s="21" t="n"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
@@ -10671,19 +10632,19 @@
     <row r="999" ht="15.75" customHeight="1">
       <c r="AN999" s="21" t="n"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" ht="14.4" customHeight="1">
       <c r="AN1000" s="21" t="n"/>
     </row>
-    <row r="1001">
+    <row r="1001" ht="14.4" customHeight="1">
       <c r="AN1001" s="21" t="n"/>
     </row>
-    <row r="1002">
+    <row r="1002" ht="14.4" customHeight="1">
       <c r="AN1002" s="21" t="n"/>
     </row>
-    <row r="1003">
+    <row r="1003" ht="14.4" customHeight="1">
       <c r="AN1003" s="21" t="n"/>
     </row>
-    <row r="1004">
+    <row r="1004" ht="14.4" customHeight="1">
       <c r="AN1004" s="21" t="n"/>
     </row>
     <row r="1005">
